--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T05:20:25+00:00</t>
+    <t>2026-09-28T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:16:57+00:00</t>
+    <t>2026-09-28T10:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:26:56+00:00</t>
+    <t>2026-09-28T11:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$88</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="592">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:29:30+00:00</t>
+    <t>2026-09-28T12:11:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,6 +96,9 @@
 - `goal` referenziert das Profil `OnkoTherapyGoal`.
 - Therapielinien (`OnkoTherapyLine`, Basis `EpisodeOfCare`) werden über die
   Standard-Extension `workflow-episodeOfCare` verknüpft.
+- `category` ist zweifach gesliced: Die Slice `erkrankungsart` trägt den ICD-10-GM-Code der
+  adressierten Tumorerkrankung. Über die Slice `therapieabschnitt` lässt sich angeben, welcher Abschnitt der Versorgung betrachtet wird,
+  beispielsweise der diagnostische (`Diagnostic intent`) oder der therapeutische (`Therapeutic intent`).
 Im Fallback-Pfad (keine computable Leitlinie) ist der CarePlan die führende Repräsentation des
 realen Versorgungsverlaufs; im Primärpfad referenziert er via `instantiatesCanonical` eine
 `PlanDefinition` aus dem CPG-on-FHIR-Stack.</t>
@@ -707,7 +710,7 @@
     <t>Planart</t>
   </si>
   <si>
-    <t>Art des Plans – proposal/plan = Empfehlungsplan des Tumorboards, plan/order = Behandlungsplan.</t>
+    <t>Art des Plans – proposal/plan = Empfehlungsplan des Tumorboards, plan/order = Behandlungs- bzw. Diagnostikplan.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -726,6 +729,9 @@
   </si>
   <si>
     <t>CarePlan.category</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -735,7 +741,7 @@
     <t>Plan-Kategorie</t>
   </si>
   <si>
-    <t>Art bzw. Kategorie des Versorgungsplans.</t>
+    <t>Kategorisierung des Versorgungsplans – Erkrankungsart mit Diagnosecode und Therapieabschnitt mit diagnostisch oder therapeutisch.</t>
   </si>
   <si>
     <t>There may be multiple axes of categorization and one plan may serve multiple purposes.  In some cases, this may be redundant with references to CarePlan.concern.</t>
@@ -753,16 +759,322 @@
     <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>CarePlan.title</t>
+    <t>CarePlan.category:erkrankungsart</t>
+  </si>
+  <si>
+    <t>erkrankungsart</t>
+  </si>
+  <si>
+    <t>Erkrankungsart</t>
+  </si>
+  <si>
+    <t>Kodierte Tumorerkrankung nach ICD-10-GM, die dieser Versorgungsplan adressiert – identisch zum Diagnosecode der referenzierten Condition.</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.id</t>
+  </si>
+  <si>
+    <t>CarePlan.category.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.category.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.system</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://fhir.de/CodeSystem/bfarm/icd-10-gm</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.version</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.code</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.display</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.coding.userSelected</t>
+  </si>
+  <si>
+    <t>CarePlan.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CarePlan.category:erkrankungsart.text</t>
+  </si>
+  <si>
+    <t>CarePlan.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt</t>
+  </si>
+  <si>
+    <t>therapieabschnitt</t>
+  </si>
+  <si>
+    <t>Therapieabschnitt</t>
+  </si>
+  <si>
+    <t>Diagnostischer oder therapeutischer Abschnitt der Versorgung – SNOMED CT Diagnostic intent 261004008 bzw. Therapeutic intent 262202000.</t>
+  </si>
+  <si>
+    <t>https://bih-cei.de/fhir/therapieziele-onkologie/ValueSet/onko-care-plan-phase</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.id</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.id</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.version</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.code</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.display</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.coding.userSelected</t>
+  </si>
+  <si>
+    <t>CarePlan.category:therapieabschnitt.text</t>
+  </si>
+  <si>
+    <t>CarePlan.title</t>
+  </si>
+  <si>
     <t>Human-friendly name for the care plan</t>
   </si>
   <si>
@@ -855,7 +1167,7 @@
     <t>Geltungszeitraum</t>
   </si>
   <si>
-    <t>Zeitraum, in dem der Versorgungsplan gültig ist.</t>
+    <t>Zeitraum, in dem der Versorgungsplan gültig ist – bei diagnostischer Nutzung der Diagnostikzeitraum von Beginn bis Diagnosesicherung.</t>
   </si>
   <si>
     <t>Any activities scheduled as part of the plan should be constrained to the specified period regardless of whether the activities are planned within a single encounter/episode or across multiple encounters/episodes (e.g. the longitudinal management of a chronic condition).</t>
@@ -961,14 +1273,14 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-condition)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-diagnose-primaertumor)
 </t>
   </si>
   <si>
     <t>Adressierte Erkrankung</t>
   </si>
   <si>
-    <t>Referenz auf die vom Plan adressierte Tumorerkrankung OnkoCondition.</t>
+    <t>Referenz auf die vom Plan adressierte Tumorerkrankung nach MII-Onkologie-Diagnoseprofil – im Diagnostikabschnitt ggf. eine Verdachtsdiagnose mit verificationStatus 'provisional' oder 'unconfirmed', die nach Diagnosesicherung auf 'confirmed' aktualisiert wird, sodass die Referenz stabil bleibt.</t>
   </si>
   <si>
     <t>When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
@@ -1021,7 +1333,7 @@
     <t>Therapieziele</t>
   </si>
   <si>
-    <t>Referenz auf die übergeordneten onkologischen Therapieziele OnkoTherapyGoal.</t>
+    <t>Referenz auf die übergeordneten onkologischen Therapie- bzw. Diagnoseziele OnkoTherapyGoal.</t>
   </si>
   <si>
     <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
@@ -1066,28 +1378,7 @@
     <t>CarePlan.activity.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>CarePlan.activity.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>CarePlan.activity.modifierExtension</t>
@@ -1399,10 +1690,6 @@
   </si>
   <si>
     <t>CarePlan.activity.detail.doNotPerform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>If true, activity is prohibiting action</t>
@@ -1902,12 +2189,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN64"/>
+  <dimension ref="A1:AN88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.58203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.27734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.5078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1930,10 +2217,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.5546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="36.58203125" customWidth="true" bestFit="true" hidden="true"/>
@@ -4348,7 +4635,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>222</v>
       </c>
@@ -4361,7 +4648,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -4376,19 +4663,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4413,28 +4700,26 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>222</v>
@@ -4458,32 +4743,34 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
@@ -4492,16 +4779,20 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4525,13 +4816,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4549,13 +4840,13 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
@@ -4570,7 +4861,7 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4578,10 +4869,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4601,21 +4892,19 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4663,7 +4952,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4675,58 +4964,60 @@
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4763,51 +5054,51 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4818,7 +5109,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4830,18 +5121,20 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4889,13 +5182,13 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
@@ -4904,28 +5197,28 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4941,23 +5234,19 @@
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5005,7 +5294,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5017,38 +5306,38 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>271</v>
+        <v>158</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5057,18 +5346,20 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>272</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5105,40 +5396,40 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -5146,10 +5437,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5157,7 +5448,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -5172,18 +5463,20 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5192,7 +5485,7 @@
         <v>80</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>80</v>
@@ -5231,7 +5524,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5246,24 +5539,24 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5274,28 +5567,28 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5345,13 +5638,13 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
@@ -5363,21 +5656,21 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5388,29 +5681,29 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5459,13 +5752,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5474,24 +5767,24 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>289</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>295</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5499,13 +5792,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
@@ -5514,19 +5807,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5581,7 +5872,7 @@
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
@@ -5590,24 +5881,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5618,31 +5909,31 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5697,7 +5988,7 @@
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -5706,24 +5997,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5734,31 +6025,31 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K34" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5807,13 +6098,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -5825,32 +6116,34 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>89</v>
@@ -5859,20 +6152,22 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>325</v>
+        <v>228</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5897,13 +6192,11 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -5921,7 +6214,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5933,16 +6226,16 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>326</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>328</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5950,10 +6243,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5976,13 +6269,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6033,7 +6326,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6051,7 +6344,7 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>333</v>
+        <v>244</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
@@ -6062,10 +6355,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6091,10 +6384,10 @@
         <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>247</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>248</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>161</v>
@@ -6135,19 +6428,19 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>250</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6165,7 +6458,7 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>244</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -6176,14 +6469,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>252</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6196,25 +6489,25 @@
         <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>254</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>255</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6263,7 +6556,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>258</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6275,27 +6568,27 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>131</v>
+        <v>259</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>262</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6306,7 +6599,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6318,17 +6611,15 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>344</v>
+        <v>241</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6353,13 +6644,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6377,25 +6668,25 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>243</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
@@ -6404,16 +6695,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>264</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6423,7 +6714,7 @@
         <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
@@ -6432,20 +6723,18 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>351</v>
+        <v>247</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>352</v>
+        <v>248</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6481,19 +6770,19 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>250</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6505,13 +6794,13 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
@@ -6522,10 +6811,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>266</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6533,10 +6822,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6545,22 +6834,22 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>267</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
+        <v>268</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>361</v>
+        <v>269</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>362</v>
+        <v>270</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6570,7 +6859,7 @@
         <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>80</v>
@@ -6609,13 +6898,13 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>272</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
@@ -6627,21 +6916,21 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>363</v>
+        <v>273</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>364</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6655,29 +6944,27 @@
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K42" t="s" s="2">
-        <v>366</v>
+        <v>240</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>367</v>
+        <v>277</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>278</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6725,7 +7012,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>365</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6734,30 +7021,30 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>284</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6777,20 +7064,20 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>322</v>
+        <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>374</v>
+        <v>285</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>375</v>
+        <v>286</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>376</v>
+        <v>287</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6839,7 +7126,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6848,7 +7135,7 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
@@ -6857,21 +7144,21 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>377</v>
+        <v>289</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6891,19 +7178,21 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>330</v>
+        <v>293</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6951,7 +7240,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6963,38 +7252,38 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>379</v>
+        <v>300</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7003,21 +7292,23 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>301</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7065,74 +7356,74 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>161</v>
+        <v>313</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7181,39 +7472,39 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>131</v>
+        <v>316</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7233,21 +7524,19 @@
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>108</v>
+        <v>240</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7271,13 +7560,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>385</v>
+        <v>80</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7295,7 +7584,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7313,7 +7602,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7324,10 +7613,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7338,7 +7627,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7347,20 +7636,20 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>389</v>
+        <v>240</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7409,13 +7698,13 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
@@ -7424,60 +7713,56 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>102</v>
+        <v>345</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>181</v>
+        <v>346</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7525,13 +7810,13 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7540,24 +7825,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>184</v>
+        <v>348</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>179</v>
+        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7577,23 +7862,21 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>223</v>
+        <v>353</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
+        <v>355</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7617,13 +7900,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7641,7 +7924,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7656,58 +7939,60 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>404</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>223</v>
+        <v>363</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>406</v>
+        <v>364</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
+        <v>365</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7731,13 +8016,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -7755,13 +8040,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -7770,35 +8055,35 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>411</v>
+        <v>368</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7807,20 +8092,18 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7869,13 +8152,13 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
@@ -7884,13 +8167,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7898,10 +8181,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7912,7 +8195,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -7921,21 +8204,21 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -7983,13 +8266,13 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
@@ -7998,24 +8281,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>385</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8023,35 +8306,33 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>381</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>424</v>
+        <v>389</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8075,13 +8356,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8099,13 +8380,13 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
@@ -8114,24 +8395,24 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8142,10 +8423,10 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
@@ -8154,18 +8435,18 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>223</v>
+        <v>392</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8213,13 +8494,13 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
@@ -8228,24 +8509,24 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>436</v>
+        <v>396</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8253,41 +8534,39 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J56" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>438</v>
+        <v>399</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
+        <v>401</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>441</v>
+        <v>402</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q56" t="s" s="2">
-        <v>443</v>
-      </c>
+      <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8331,13 +8610,13 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
@@ -8346,24 +8625,24 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>444</v>
+        <v>404</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>80</v>
+        <v>406</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>80</v>
+        <v>407</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8374,10 +8653,10 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>80</v>
@@ -8386,17 +8665,19 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>450</v>
+        <v>413</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8445,13 +8726,13 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
@@ -8460,24 +8741,24 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>266</v>
+        <v>414</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>267</v>
+        <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>451</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8488,10 +8769,10 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>80</v>
@@ -8500,19 +8781,19 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8561,13 +8842,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -8579,21 +8860,21 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>459</v>
+        <v>422</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8607,7 +8888,7 @@
         <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -8616,19 +8897,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8677,7 +8956,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8689,27 +8968,27 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>428</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>467</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8732,13 +9011,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>469</v>
+        <v>240</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>470</v>
+        <v>241</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>471</v>
+        <v>242</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8765,13 +9044,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8789,7 +9068,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>468</v>
+        <v>243</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8801,38 +9080,38 @@
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>474</v>
+        <v>244</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>475</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>477</v>
+        <v>158</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -8844,18 +9123,18 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>478</v>
+        <v>133</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>479</v>
+        <v>247</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8903,71 +9182,75 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>476</v>
+        <v>250</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>482</v>
+        <v>244</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>483</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>80</v>
+        <v>434</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>478</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>485</v>
+        <v>435</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9015,39 +9298,39 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>487</v>
+        <v>131</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>488</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9058,7 +9341,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
@@ -9070,15 +9353,17 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>490</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9103,13 +9388,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9127,13 +9412,13 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
@@ -9145,21 +9430,21 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>492</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9173,7 +9458,7 @@
         <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>80</v>
@@ -9182,17 +9467,19 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>358</v>
+        <v>445</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>496</v>
+        <v>449</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9241,7 +9528,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9256,20 +9543,2768 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK74" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>364</v>
+      <c r="AL74" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q80" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="R80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN64">
+  <autoFilter ref="A1:AN88">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9279,7 +12314,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI87">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:11:39+00:00</t>
+    <t>2026-09-28T20:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T20:57:11+00:00</t>
+    <t>2026-09-28T21:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:01:12+00:00</t>
+    <t>2026-09-30T11:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:29:35+00:00</t>
+    <t>2026-10-01T05:55:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,7 +94,7 @@
 - Therapieintention über die Extension `onko-therapy-intent` (kurativ, neoadjuvant, adjuvant,
   Erhaltung, palliativ, supportiv).
 - `goal` referenziert das Profil `OnkoTherapyGoal`.
-- Therapielinien (`OnkoTherapyLine`, Basis `EpisodeOfCare`) werden über die
+- Behandlungsepisoden (`OnkoBehandlungsepisode`, Basis `EpisodeOfCare`) werden über die
   Standard-Extension `workflow-episodeOfCare` verknüpft.
 - `category` ist zweifach gesliced: Die Slice `erkrankungsart` trägt den ICD-10-GM-Code der
   adressierten Tumorerkrankung. Über die Slice `therapieabschnitt` lässt sich angeben, welcher Abschnitt der Versorgung betrachtet wird,

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-care-plan.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
